--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1434544150879677</v>
+        <v>-0.001256861252955876</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2717041464316365</v>
+        <v>0.1680945583038038</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.6381880391369809</v>
+        <v>-0.01312475068068697</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.9290816982180359</v>
+        <v>-0.01790115619041825</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2138375433014859</v>
+        <v>0.12742404350528</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.7648939356020235</v>
+        <v>-0.01114541198287915</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>33.66663140688117</v>
+        <v>40.66177311370343</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.260340609313639</v>
+        <v>0.04125573381138881</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2356471039045673</v>
+        <v>0.2822737009690121</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.277252788691835</v>
+        <v>0.2363484380779888</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.677842420430051</v>
+        <v>0.3535008060315767</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3167468698000422</v>
+        <v>0.1835298258981255</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8508390224761379</v>
+        <v>0.2342761559456055</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>41.59545650427963</v>
+        <v>24.88204288720442</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.06579716883481368</v>
+        <v>0.006213212407637059</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2148899317973602</v>
+        <v>0.2317055123023402</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.2921049354340896</v>
+        <v>0.07887002479280053</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.4165286609904047</v>
+        <v>0.1126164363464919</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2235983226949688</v>
+        <v>0.206858000294574</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.305999129627871</v>
+        <v>0.03128129263076643</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>45.19113327692273</v>
+        <v>61.19279510724555</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1074451819408249</v>
+        <v>0.02425322820814113</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2243208978512146</v>
+        <v>0.2479661297799408</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5189243559798675</v>
+        <v>0.164240019417224</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.7694879456543656</v>
+        <v>0.2283324184374262</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1280442335488264</v>
+        <v>0.1638912641992324</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.8756765897131755</v>
+        <v>0.1541753088368424</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>42.51896679316594</v>
+        <v>46.20550163567209</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2320537154978728</v>
+        <v>0.3407286730553345</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2421526556151342</v>
+        <v>0.2582049894415337</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.9537806688147225</v>
+        <v>1.25054210230173</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.345295623377344</v>
+        <v>1.739522018450713</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1582525649390213</v>
+        <v>0.1278746023852052</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.526756479356432</v>
+        <v>2.779035012133467</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>53.33576019192106</v>
+        <v>52.246620353046</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.2451845300020832</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3695953955928007</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1.219316219404612</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1.849491635927514</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.1532262024790755</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3.185974353345046</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>41.31027831197328</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>